--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-temperature.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -217,13 +217,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -234,9 +430,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Observation.language</t>
@@ -319,38 +512,10 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Observation.extension:levelOfExertion</t>
@@ -583,39 +748,16 @@
     <t>Observation.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -836,9 +978,6 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
@@ -1064,10 +1203,6 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -1423,9 +1558,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>http://models.opencimi.org/ig/vital-signs-fhir-profiles/ValueSet-bodyTempMeasBodyLocationPrecoordVS.html</t>
@@ -2174,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP84"/>
+  <dimension ref="A1:AP93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
@@ -2200,7 +2332,7 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="101.08984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
@@ -2599,10 +2731,10 @@
         <v>38</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>65</v>
@@ -2613,9 +2745,7 @@
       <c r="M4" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>38</v>
@@ -2664,7 +2794,7 @@
         <v>38</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
@@ -2673,10 +2803,10 @@
         <v>49</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>38</v>
@@ -2688,7 +2818,7 @@
         <v>38</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>38</v>
@@ -2699,21 +2829,21 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>38</v>
@@ -2760,28 +2890,28 @@
         <v>38</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>79</v>
@@ -2790,13 +2920,13 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>38</v>
@@ -2808,7 +2938,7 @@
         <v>38</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>38</v>
@@ -2819,14 +2949,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2842,19 +2972,19 @@
         <v>38</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2904,7 +3034,7 @@
         <v>38</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2928,7 +3058,7 @@
         <v>38</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>38</v>
@@ -2939,21 +3069,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>38</v>
@@ -2962,19 +3092,19 @@
         <v>38</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3024,19 +3154,19 @@
         <v>38</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>38</v>
@@ -3048,7 +3178,7 @@
         <v>38</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>38</v>
@@ -3059,21 +3189,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>38</v>
@@ -3082,19 +3212,19 @@
         <v>38</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3132,31 +3262,31 @@
         <v>38</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>38</v>
@@ -3168,7 +3298,7 @@
         <v>38</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>38</v>
@@ -3179,14 +3309,12 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>38</v>
       </c>
@@ -3195,7 +3323,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>38</v>
@@ -3204,18 +3332,20 @@
         <v>38</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>38</v>
@@ -3252,19 +3382,19 @@
         <v>38</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -3276,7 +3406,7 @@
         <v>61</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>38</v>
@@ -3288,7 +3418,7 @@
         <v>38</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>38</v>
@@ -3299,13 +3429,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>38</v>
@@ -3318,24 +3448,26 @@
         <v>49</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>38</v>
@@ -3345,7 +3477,7 @@
         <v>38</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>38</v>
@@ -3384,7 +3516,7 @@
         <v>38</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -3396,7 +3528,7 @@
         <v>61</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>38</v>
@@ -3408,7 +3540,7 @@
         <v>38</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>38</v>
@@ -3419,14 +3551,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3439,26 +3571,24 @@
         <v>38</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>38</v>
       </c>
@@ -3482,31 +3612,31 @@
         <v>38</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>36</v>
@@ -3518,7 +3648,7 @@
         <v>61</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>38</v>
@@ -3527,10 +3657,10 @@
         <v>38</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>38</v>
@@ -3541,10 +3671,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3567,18 +3697,18 @@
         <v>50</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>125</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>38</v>
       </c>
@@ -3602,13 +3732,13 @@
         <v>38</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>38</v>
@@ -3626,7 +3756,7 @@
         <v>38</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3641,19 +3771,19 @@
         <v>62</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>38</v>
@@ -3661,46 +3791,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>38</v>
       </c>
@@ -3748,31 +3876,31 @@
         <v>38</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>38</v>
@@ -3783,21 +3911,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>38</v>
@@ -3806,19 +3934,19 @@
         <v>38</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3844,13 +3972,13 @@
         <v>38</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>38</v>
@@ -3868,31 +3996,31 @@
         <v>38</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>38</v>
@@ -3903,46 +4031,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>38</v>
       </c>
@@ -3966,13 +4092,13 @@
         <v>38</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>38</v>
@@ -3990,10 +4116,10 @@
         <v>38</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>49</v>
@@ -4005,19 +4131,19 @@
         <v>62</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>158</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>38</v>
@@ -4025,24 +4151,24 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>38</v>
@@ -4051,20 +4177,18 @@
         <v>38</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>38</v>
       </c>
@@ -4088,29 +4212,31 @@
         <v>38</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AC16" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -4119,10 +4245,10 @@
         <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>38</v>
@@ -4131,13 +4257,13 @@
         <v>38</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>38</v>
@@ -4145,26 +4271,24 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>38</v>
@@ -4173,20 +4297,18 @@
         <v>38</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>38</v>
       </c>
@@ -4210,31 +4332,31 @@
         <v>38</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB17" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="AC17" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -4246,7 +4368,7 @@
         <v>61</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>38</v>
@@ -4255,13 +4377,13 @@
         <v>38</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>174</v>
+        <v>38</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>38</v>
@@ -4269,12 +4391,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>38</v>
       </c>
@@ -4295,13 +4419,13 @@
         <v>38</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4352,19 +4476,19 @@
         <v>38</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>38</v>
@@ -4376,7 +4500,7 @@
         <v>38</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>38</v>
@@ -4387,24 +4511,26 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>38</v>
@@ -4413,17 +4539,15 @@
         <v>38</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>38</v>
@@ -4460,19 +4584,19 @@
         <v>38</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -4484,7 +4608,7 @@
         <v>61</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>38</v>
@@ -4507,45 +4631,45 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>189</v>
+        <v>72</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>38</v>
@@ -4582,19 +4706,19 @@
         <v>38</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>36</v>
@@ -4606,7 +4730,7 @@
         <v>61</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>38</v>
@@ -4615,10 +4739,10 @@
         <v>38</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>38</v>
@@ -4629,10 +4753,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4643,7 +4767,7 @@
         <v>36</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>38</v>
@@ -4652,19 +4776,21 @@
         <v>38</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>38</v>
       </c>
@@ -4712,34 +4838,34 @@
         <v>38</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>38</v>
@@ -4747,14 +4873,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4770,21 +4896,23 @@
         <v>38</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>38</v>
       </c>
@@ -4820,19 +4948,19 @@
         <v>38</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4844,19 +4972,19 @@
         <v>61</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>38</v>
@@ -4867,24 +4995,24 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>38</v>
@@ -4893,26 +5021,24 @@
         <v>50</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>207</v>
+        <v>38</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>38</v>
@@ -4954,31 +5080,31 @@
         <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>38</v>
@@ -4989,10 +5115,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5000,33 +5126,35 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>38</v>
       </c>
@@ -5050,13 +5178,13 @@
         <v>38</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>38</v>
+        <v>209</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>38</v>
@@ -5074,10 +5202,10 @@
         <v>38</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>49</v>
@@ -5089,19 +5217,19 @@
         <v>62</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>38</v>
+        <v>211</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>38</v>
+        <v>215</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>38</v>
@@ -5109,10 +5237,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5123,7 +5251,7 @@
         <v>49</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>50</v>
@@ -5132,29 +5260,29 @@
         <v>38</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>225</v>
+        <v>38</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>38</v>
@@ -5172,37 +5300,35 @@
         <v>38</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>38</v>
+        <v>223</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>61</v>
@@ -5217,13 +5343,13 @@
         <v>38</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>38</v>
@@ -5231,45 +5357,47 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>38</v>
@@ -5294,13 +5422,13 @@
         <v>38</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>38</v>
+        <v>223</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>38</v>
@@ -5318,13 +5446,13 @@
         <v>38</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>61</v>
@@ -5339,13 +5467,13 @@
         <v>38</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>38</v>
+        <v>227</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>38</v>
@@ -5353,10 +5481,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5376,23 +5504,19 @@
         <v>38</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>239</v>
+        <v>65</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>38</v>
       </c>
@@ -5440,7 +5564,7 @@
         <v>38</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>68</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -5449,10 +5573,10 @@
         <v>49</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>38</v>
@@ -5461,10 +5585,10 @@
         <v>38</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>246</v>
+        <v>69</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>38</v>
@@ -5475,21 +5599,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>38</v>
@@ -5498,23 +5622,21 @@
         <v>38</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>38</v>
       </c>
@@ -5550,31 +5672,31 @@
         <v>38</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>38</v>
@@ -5583,10 +5705,10 @@
         <v>38</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>38</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>255</v>
+        <v>63</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>38</v>
@@ -5597,21 +5719,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>49</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>50</v>
@@ -5623,19 +5745,19 @@
         <v>50</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>38</v>
@@ -5660,13 +5782,13 @@
         <v>38</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>263</v>
+        <v>38</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>38</v>
@@ -5684,13 +5806,13 @@
         <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>61</v>
@@ -5699,30 +5821,30 @@
         <v>62</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>265</v>
+        <v>38</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>266</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>269</v>
+        <v>38</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>270</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5745,13 +5867,13 @@
         <v>38</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5802,7 +5924,7 @@
         <v>38</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5826,7 +5948,7 @@
         <v>38</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>38</v>
@@ -5837,14 +5959,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5863,16 +5985,16 @@
         <v>38</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5910,19 +6032,19 @@
         <v>38</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
@@ -5934,7 +6056,7 @@
         <v>61</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>38</v>
@@ -5957,10 +6079,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5968,13 +6090,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>38</v>
@@ -5983,26 +6105,26 @@
         <v>50</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>38</v>
@@ -6032,23 +6154,25 @@
         <v>38</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>254</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>61</v>
@@ -6063,10 +6187,10 @@
         <v>38</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>195</v>
+        <v>255</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>38</v>
@@ -6077,20 +6201,18 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>49</v>
@@ -6105,20 +6227,18 @@
         <v>50</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>38</v>
       </c>
@@ -6166,13 +6286,13 @@
         <v>38</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>61</v>
@@ -6187,10 +6307,10 @@
         <v>38</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>38</v>
@@ -6201,10 +6321,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6212,37 +6332,41 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>38</v>
+        <v>271</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>38</v>
@@ -6284,7 +6408,7 @@
         <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
@@ -6293,10 +6417,10 @@
         <v>49</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>38</v>
@@ -6305,10 +6429,10 @@
         <v>38</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>70</v>
+        <v>274</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>38</v>
@@ -6319,21 +6443,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>38</v>
@@ -6342,21 +6466,23 @@
         <v>38</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>98</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>38</v>
       </c>
@@ -6392,31 +6518,31 @@
         <v>38</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>38</v>
@@ -6425,10 +6551,10 @@
         <v>38</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>38</v>
+        <v>281</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>63</v>
+        <v>282</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>38</v>
@@ -6439,10 +6565,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6450,7 +6576,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>49</v>
@@ -6465,26 +6591,26 @@
         <v>50</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>65</v>
+        <v>285</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>203</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>204</v>
+        <v>287</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>205</v>
+        <v>288</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>206</v>
+        <v>289</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>38</v>
@@ -6526,7 +6652,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6547,10 +6673,10 @@
         <v>38</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>38</v>
@@ -6561,10 +6687,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6587,18 +6713,20 @@
         <v>50</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>214</v>
+        <v>296</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>38</v>
       </c>
@@ -6646,7 +6774,7 @@
         <v>38</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>36</v>
@@ -6667,10 +6795,10 @@
         <v>38</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>217</v>
+        <v>300</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>38</v>
@@ -6681,14 +6809,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6698,7 +6826,7 @@
         <v>49</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>38</v>
@@ -6707,26 +6835,26 @@
         <v>50</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>222</v>
+        <v>305</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>223</v>
+        <v>306</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>224</v>
+        <v>307</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>288</v>
+        <v>38</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>38</v>
@@ -6744,13 +6872,13 @@
         <v>38</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>38</v>
+        <v>308</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>38</v>
+        <v>309</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>38</v>
@@ -6768,10 +6896,10 @@
         <v>38</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>49</v>
@@ -6783,30 +6911,30 @@
         <v>62</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>38</v>
+        <v>310</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>38</v>
+        <v>311</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>38</v>
+        <v>314</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>38</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6826,23 +6954,19 @@
         <v>38</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>231</v>
+        <v>66</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>38</v>
       </c>
@@ -6890,7 +7014,7 @@
         <v>38</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>234</v>
+        <v>68</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
@@ -6899,10 +7023,10 @@
         <v>49</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>38</v>
@@ -6911,10 +7035,10 @@
         <v>38</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>235</v>
+        <v>38</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>38</v>
@@ -6925,21 +7049,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>38</v>
@@ -6948,23 +7072,21 @@
         <v>38</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>241</v>
+        <v>74</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>38</v>
       </c>
@@ -7000,31 +7122,31 @@
         <v>38</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>38</v>
@@ -7033,10 +7155,10 @@
         <v>38</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>246</v>
+        <v>63</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>38</v>
@@ -7047,10 +7169,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7061,7 +7183,7 @@
         <v>36</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>38</v>
@@ -7073,19 +7195,19 @@
         <v>50</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>38</v>
@@ -7122,25 +7244,23 @@
         <v>38</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>61</v>
@@ -7155,10 +7275,10 @@
         <v>38</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>38</v>
@@ -7169,12 +7289,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>38</v>
       </c>
@@ -7186,7 +7308,7 @@
         <v>49</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>38</v>
@@ -7195,19 +7317,19 @@
         <v>50</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>38</v>
@@ -7256,34 +7378,34 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>300</v>
+        <v>38</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>303</v>
+        <v>38</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>38</v>
@@ -7291,10 +7413,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7305,7 +7427,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>38</v>
@@ -7314,20 +7436,18 @@
         <v>38</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>305</v>
+        <v>65</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>66</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>38</v>
@@ -7376,19 +7496,19 @@
         <v>38</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>304</v>
+        <v>68</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>38</v>
@@ -7397,13 +7517,13 @@
         <v>38</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>309</v>
+        <v>69</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>303</v>
+        <v>38</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>38</v>
@@ -7411,21 +7531,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>311</v>
+        <v>71</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>38</v>
@@ -7434,23 +7554,21 @@
         <v>38</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>312</v>
+        <v>72</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>73</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>74</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>38</v>
       </c>
@@ -7486,46 +7604,46 @@
         <v>38</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>318</v>
+        <v>38</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>319</v>
+        <v>63</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>320</v>
+        <v>38</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>38</v>
@@ -7533,14 +7651,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>322</v>
+        <v>38</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7550,7 +7668,7 @@
         <v>49</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>38</v>
@@ -7559,26 +7677,26 @@
         <v>50</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>323</v>
+        <v>93</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>38</v>
@@ -7620,7 +7738,7 @@
         <v>38</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>254</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -7629,25 +7747,25 @@
         <v>49</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>328</v>
+        <v>61</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>329</v>
+        <v>62</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>330</v>
+        <v>38</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>332</v>
+        <v>256</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>333</v>
+        <v>38</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>38</v>
@@ -7655,10 +7773,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7681,16 +7799,16 @@
         <v>50</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>335</v>
+        <v>65</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>338</v>
+        <v>261</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7740,7 +7858,7 @@
         <v>38</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
@@ -7761,13 +7879,13 @@
         <v>38</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>38</v>
@@ -7775,10 +7893,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7786,10 +7904,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>38</v>
@@ -7801,26 +7919,26 @@
         <v>50</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>343</v>
+        <v>133</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>344</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>345</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>135</v>
+        <v>269</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>346</v>
+        <v>270</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>38</v>
@@ -7862,34 +7980,34 @@
         <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>38</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>348</v>
+        <v>273</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>350</v>
+        <v>38</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>38</v>
@@ -7897,10 +8015,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7914,7 +8032,7 @@
         <v>49</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>38</v>
@@ -7923,19 +8041,19 @@
         <v>50</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>352</v>
+        <v>65</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>354</v>
+        <v>269</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>38</v>
@@ -7972,17 +8090,19 @@
         <v>38</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>357</v>
+        <v>38</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>351</v>
+        <v>280</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7991,7 +8111,7 @@
         <v>49</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>358</v>
+        <v>61</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>62</v>
@@ -8000,31 +8120,29 @@
         <v>38</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>38</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>360</v>
+        <v>281</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>362</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>38</v>
       </c>
@@ -8036,7 +8154,7 @@
         <v>49</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>38</v>
@@ -8045,19 +8163,19 @@
         <v>50</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>365</v>
+        <v>285</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>38</v>
@@ -8106,7 +8224,7 @@
         <v>38</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -8115,7 +8233,7 @@
         <v>49</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>358</v>
+        <v>61</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>62</v>
@@ -8124,27 +8242,27 @@
         <v>38</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>38</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>360</v>
+        <v>291</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>362</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8164,19 +8282,23 @@
         <v>38</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>180</v>
+        <v>295</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>38</v>
       </c>
@@ -8224,7 +8346,7 @@
         <v>38</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
@@ -8233,10 +8355,10 @@
         <v>49</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>38</v>
@@ -8245,10 +8367,10 @@
         <v>38</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>38</v>
+        <v>300</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>70</v>
+        <v>301</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>38</v>
@@ -8259,44 +8381,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>341</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>342</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>38</v>
       </c>
@@ -8332,46 +8456,46 @@
         <v>38</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>186</v>
+        <v>339</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>38</v>
+        <v>345</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>38</v>
+        <v>346</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>38</v>
+        <v>348</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>38</v>
@@ -8379,10 +8503,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8390,13 +8514,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>38</v>
@@ -8405,20 +8529,18 @@
         <v>50</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>38</v>
       </c>
@@ -8466,19 +8588,19 @@
         <v>38</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>38</v>
@@ -8487,13 +8609,13 @@
         <v>38</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>378</v>
+        <v>312</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>38</v>
+        <v>348</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>38</v>
@@ -8501,14 +8623,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>38</v>
+        <v>356</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8521,32 +8643,30 @@
         <v>38</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>72</v>
+        <v>357</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>223</v>
+        <v>360</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="Q53" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
         <v>38</v>
       </c>
@@ -8566,13 +8686,13 @@
         <v>38</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>386</v>
+        <v>38</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>387</v>
+        <v>38</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>38</v>
@@ -8590,7 +8710,7 @@
         <v>38</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -8602,22 +8722,22 @@
         <v>61</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>38</v>
+        <v>362</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>38</v>
+        <v>365</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>38</v>
@@ -8625,14 +8745,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>38</v>
+        <v>367</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8651,19 +8771,19 @@
         <v>50</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>223</v>
+        <v>371</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>38</v>
@@ -8712,7 +8832,7 @@
         <v>38</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8721,25 +8841,25 @@
         <v>49</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>61</v>
+        <v>373</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>38</v>
+        <v>375</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>38</v>
+        <v>378</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>38</v>
@@ -8747,10 +8867,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8758,13 +8878,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>38</v>
@@ -8773,26 +8893,24 @@
         <v>50</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>405</v>
+        <v>38</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>38</v>
@@ -8834,7 +8952,7 @@
         <v>38</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
@@ -8843,7 +8961,7 @@
         <v>49</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>407</v>
+        <v>61</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>62</v>
@@ -8855,13 +8973,13 @@
         <v>38</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>38</v>
+        <v>385</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>38</v>
@@ -8869,10 +8987,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8880,13 +8998,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>38</v>
@@ -8895,19 +9013,19 @@
         <v>50</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>72</v>
+        <v>387</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>412</v>
+        <v>188</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>38</v>
@@ -8932,13 +9050,13 @@
         <v>38</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>414</v>
+        <v>38</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>415</v>
+        <v>38</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>38</v>
@@ -8956,34 +9074,34 @@
         <v>38</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>38</v>
+        <v>391</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>38</v>
+        <v>394</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>38</v>
@@ -8991,10 +9109,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9014,22 +9132,22 @@
         <v>38</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>164</v>
+        <v>396</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>38</v>
@@ -9054,31 +9172,29 @@
         <v>38</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>423</v>
+        <v>38</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>38</v>
+        <v>401</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
@@ -9087,7 +9203,7 @@
         <v>49</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>62</v>
@@ -9096,62 +9212,64 @@
         <v>38</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>63</v>
+        <v>404</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>38</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="D58" t="s" s="2">
-        <v>428</v>
+        <v>38</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>164</v>
+        <v>409</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>398</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>38</v>
@@ -9176,13 +9294,13 @@
         <v>38</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>434</v>
+        <v>38</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>38</v>
@@ -9200,16 +9318,16 @@
         <v>38</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>61</v>
+        <v>402</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>62</v>
@@ -9218,27 +9336,27 @@
         <v>38</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>438</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9249,7 +9367,7 @@
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>38</v>
@@ -9261,20 +9379,16 @@
         <v>38</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>66</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>38</v>
       </c>
@@ -9322,19 +9436,19 @@
         <v>38</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>439</v>
+        <v>68</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>38</v>
@@ -9343,10 +9457,10 @@
         <v>38</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>445</v>
+        <v>38</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>446</v>
+        <v>69</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>38</v>
@@ -9357,21 +9471,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>447</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>38</v>
@@ -9383,16 +9497,16 @@
         <v>38</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>164</v>
+        <v>72</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>73</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
+        <v>74</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9418,67 +9532,69 @@
         <v>38</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>452</v>
+        <v>38</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>447</v>
+        <v>79</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>453</v>
+        <v>38</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>454</v>
+        <v>38</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>455</v>
+        <v>63</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>456</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9486,34 +9602,34 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>164</v>
+        <v>416</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>38</v>
@@ -9538,13 +9654,13 @@
         <v>38</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>451</v>
+        <v>38</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>462</v>
+        <v>38</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>463</v>
+        <v>38</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>38</v>
@@ -9562,7 +9678,7 @@
         <v>38</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -9583,10 +9699,10 @@
         <v>38</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>38</v>
@@ -9597,10 +9713,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9617,28 +9733,32 @@
         <v>38</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>467</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
+        <v>427</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="R62" t="s" s="2">
         <v>38</v>
       </c>
@@ -9658,13 +9778,13 @@
         <v>38</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>38</v>
+        <v>430</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>38</v>
+        <v>431</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>38</v>
@@ -9682,7 +9802,7 @@
         <v>38</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -9694,33 +9814,33 @@
         <v>61</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>471</v>
+        <v>38</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>472</v>
+        <v>433</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>473</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>474</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>475</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9728,33 +9848,35 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>476</v>
+        <v>65</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>477</v>
+        <v>437</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>38</v>
       </c>
@@ -9802,7 +9924,7 @@
         <v>38</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>475</v>
+        <v>440</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -9814,33 +9936,33 @@
         <v>61</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>480</v>
+        <v>38</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>483</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9848,41 +9970,41 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>485</v>
+        <v>93</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>486</v>
+        <v>445</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>38</v>
+        <v>449</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>38</v>
@@ -9924,19 +10046,19 @@
         <v>38</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>61</v>
+        <v>451</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>490</v>
+        <v>62</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>38</v>
@@ -9945,10 +10067,10 @@
         <v>38</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>491</v>
+        <v>441</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>38</v>
@@ -9959,10 +10081,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9970,31 +10092,35 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>180</v>
+        <v>455</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>38</v>
       </c>
@@ -10018,13 +10144,13 @@
         <v>38</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>38</v>
+        <v>458</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>38</v>
+        <v>459</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>38</v>
@@ -10042,7 +10168,7 @@
         <v>38</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>182</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -10051,10 +10177,10 @@
         <v>49</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>38</v>
@@ -10063,10 +10189,10 @@
         <v>38</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>38</v>
+        <v>441</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>38</v>
@@ -10077,24 +10203,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>38</v>
@@ -10103,18 +10229,20 @@
         <v>38</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>98</v>
+        <v>463</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>185</v>
+        <v>464</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>38</v>
       </c>
@@ -10138,43 +10266,43 @@
         <v>38</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>38</v>
+        <v>468</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>186</v>
+        <v>462</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>61</v>
+        <v>469</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>38</v>
@@ -10183,10 +10311,10 @@
         <v>38</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>63</v>
+        <v>470</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>38</v>
@@ -10197,14 +10325,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10217,25 +10345,25 @@
         <v>38</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>119</v>
+        <v>476</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>38</v>
@@ -10260,13 +10388,13 @@
         <v>38</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>38</v>
+        <v>477</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>38</v>
+        <v>478</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>38</v>
@@ -10284,7 +10412,7 @@
         <v>38</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
@@ -10296,33 +10424,33 @@
         <v>61</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>38</v>
+        <v>479</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>38</v>
+        <v>480</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>63</v>
+        <v>481</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>38</v>
+        <v>482</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10333,7 +10461,7 @@
         <v>36</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>38</v>
@@ -10345,18 +10473,20 @@
         <v>38</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>38</v>
       </c>
@@ -10404,19 +10534,19 @@
         <v>38</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>505</v>
+        <v>61</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>506</v>
+        <v>62</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>38</v>
@@ -10425,10 +10555,10 @@
         <v>38</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>38</v>
@@ -10439,10 +10569,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10465,16 +10595,16 @@
         <v>38</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>501</v>
+        <v>217</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10500,13 +10630,11 @@
         <v>38</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>38</v>
+        <v>495</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>38</v>
@@ -10524,7 +10652,7 @@
         <v>38</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -10533,36 +10661,36 @@
         <v>49</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>505</v>
+        <v>61</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>506</v>
+        <v>62</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>38</v>
+        <v>496</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>38</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10585,19 +10713,19 @@
         <v>38</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>38</v>
@@ -10622,13 +10750,13 @@
         <v>38</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>38</v>
@@ -10646,7 +10774,7 @@
         <v>38</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
@@ -10664,13 +10792,13 @@
         <v>38</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>520</v>
+        <v>38</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>437</v>
+        <v>508</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>38</v>
@@ -10681,10 +10809,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10695,7 +10823,7 @@
         <v>36</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>38</v>
@@ -10707,20 +10835,18 @@
         <v>38</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>164</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>38</v>
       </c>
@@ -10744,13 +10870,13 @@
         <v>38</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>451</v>
+        <v>38</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>527</v>
+        <v>38</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>528</v>
+        <v>38</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>38</v>
@@ -10768,45 +10894,45 @@
         <v>38</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>437</v>
+        <v>516</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>38</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10829,20 +10955,18 @@
         <v>38</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>38</v>
       </c>
@@ -10890,7 +11014,7 @@
         <v>38</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -10902,33 +11026,33 @@
         <v>61</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>535</v>
+        <v>190</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>38</v>
+        <v>523</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>38</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10939,7 +11063,7 @@
         <v>36</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>38</v>
@@ -10951,18 +11075,20 @@
         <v>38</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>179</v>
+        <v>528</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>38</v>
       </c>
@@ -11010,19 +11136,19 @@
         <v>38</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>62</v>
+        <v>533</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>38</v>
@@ -11031,10 +11157,10 @@
         <v>38</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>38</v>
@@ -11045,10 +11171,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11059,7 +11185,7 @@
         <v>36</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>38</v>
@@ -11068,20 +11194,18 @@
         <v>38</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>543</v>
+        <v>65</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>544</v>
+        <v>66</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>38</v>
@@ -11130,19 +11254,19 @@
         <v>38</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>542</v>
+        <v>68</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>38</v>
@@ -11151,10 +11275,10 @@
         <v>38</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>547</v>
+        <v>38</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>548</v>
+        <v>69</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>38</v>
@@ -11165,14 +11289,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11188,19 +11312,19 @@
         <v>38</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>550</v>
+        <v>72</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>551</v>
+        <v>73</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>552</v>
+        <v>74</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>553</v>
+        <v>75</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11238,19 +11362,19 @@
         <v>38</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11262,7 +11386,7 @@
         <v>61</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>38</v>
@@ -11271,10 +11395,10 @@
         <v>38</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>547</v>
+        <v>38</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>554</v>
+        <v>63</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>38</v>
@@ -11285,14 +11409,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>38</v>
+        <v>539</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11302,28 +11426,28 @@
         <v>37</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I76" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>485</v>
+        <v>72</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>557</v>
+        <v>75</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>558</v>
+        <v>172</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>38</v>
@@ -11372,7 +11496,7 @@
         <v>38</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -11384,7 +11508,7 @@
         <v>61</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>559</v>
+        <v>80</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>38</v>
@@ -11393,10 +11517,10 @@
         <v>38</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>560</v>
+        <v>38</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>561</v>
+        <v>63</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>38</v>
@@ -11407,10 +11531,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11433,15 +11557,17 @@
         <v>38</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>179</v>
+        <v>544</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>180</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>38</v>
@@ -11490,7 +11616,7 @@
         <v>38</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>182</v>
+        <v>543</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -11499,10 +11625,10 @@
         <v>49</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>38</v>
+        <v>548</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>38</v>
+        <v>549</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>38</v>
@@ -11511,10 +11637,10 @@
         <v>38</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>38</v>
+        <v>550</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>70</v>
+        <v>551</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>38</v>
@@ -11525,21 +11651,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>38</v>
@@ -11551,16 +11677,16 @@
         <v>38</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>97</v>
+        <v>544</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>98</v>
+        <v>553</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>185</v>
+        <v>554</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>100</v>
+        <v>547</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11598,31 +11724,31 @@
         <v>38</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>186</v>
+        <v>552</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>61</v>
+        <v>548</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>105</v>
+        <v>549</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>38</v>
@@ -11631,10 +11757,10 @@
         <v>38</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>38</v>
+        <v>550</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>63</v>
+        <v>555</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>38</v>
@@ -11645,45 +11771,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>496</v>
+        <v>38</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>498</v>
+        <v>558</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>100</v>
+        <v>559</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>119</v>
+        <v>560</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>38</v>
@@ -11708,13 +11834,13 @@
         <v>38</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>38</v>
+        <v>561</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>38</v>
+        <v>562</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>38</v>
@@ -11732,31 +11858,31 @@
         <v>38</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>556</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>38</v>
+        <v>563</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>38</v>
+        <v>564</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>63</v>
+        <v>481</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>38</v>
@@ -11778,22 +11904,22 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>566</v>
@@ -11830,13 +11956,13 @@
         <v>38</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>262</v>
+        <v>123</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>263</v>
+        <v>570</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>264</v>
+        <v>571</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>38</v>
@@ -11857,10 +11983,10 @@
         <v>565</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>61</v>
@@ -11872,16 +11998,16 @@
         <v>38</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>267</v>
+        <v>564</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>268</v>
+        <v>481</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>269</v>
+        <v>38</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>38</v>
@@ -11889,10 +12015,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11906,28 +12032,28 @@
         <v>49</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>352</v>
+        <v>573</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>355</v>
+        <v>577</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>38</v>
@@ -11952,13 +12078,13 @@
         <v>38</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>575</v>
+        <v>38</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>576</v>
+        <v>38</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>38</v>
@@ -11976,7 +12102,7 @@
         <v>38</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -11985,36 +12111,36 @@
         <v>49</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>577</v>
+        <v>61</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>62</v>
+        <v>578</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>578</v>
+        <v>38</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>360</v>
+        <v>579</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>361</v>
+        <v>580</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>362</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12028,7 +12154,7 @@
         <v>49</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>38</v>
@@ -12037,20 +12163,18 @@
         <v>38</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>38</v>
       </c>
@@ -12074,13 +12198,13 @@
         <v>38</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>423</v>
+        <v>38</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>424</v>
+        <v>38</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>38</v>
@@ -12098,7 +12222,7 @@
         <v>38</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -12107,7 +12231,7 @@
         <v>49</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>583</v>
+        <v>61</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>62</v>
@@ -12119,10 +12243,10 @@
         <v>38</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>63</v>
+        <v>550</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>426</v>
+        <v>584</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>38</v>
@@ -12133,14 +12257,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>428</v>
+        <v>38</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12156,23 +12280,21 @@
         <v>38</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>164</v>
+        <v>586</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>429</v>
+        <v>587</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>430</v>
+        <v>588</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>38</v>
       </c>
@@ -12196,13 +12318,13 @@
         <v>38</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>433</v>
+        <v>38</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>434</v>
+        <v>38</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>38</v>
@@ -12220,7 +12342,7 @@
         <v>38</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
@@ -12232,33 +12354,33 @@
         <v>61</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>435</v>
+        <v>38</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>436</v>
+        <v>590</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>437</v>
+        <v>591</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>438</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12278,23 +12400,21 @@
         <v>38</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>39</v>
+        <v>593</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>38</v>
       </c>
@@ -12342,7 +12462,7 @@
         <v>38</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
@@ -12351,10 +12471,10 @@
         <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>38</v>
@@ -12363,20 +12483,1112 @@
         <v>38</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>491</v>
+        <v>590</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>492</v>
+        <v>597</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP84" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP84">
+  <autoFilter ref="A1:AP93">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12386,7 +13598,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
